--- a/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_Order_by_Sample_Layer.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_Order_by_Sample_Layer.xlsx
@@ -676,10 +676,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>22.0698890283973</v>
+        <v>22.07717672444</v>
       </c>
       <c r="D2" t="n">
-        <v>1.17872018799861</v>
+        <v>1.17929120251656</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>17.4383623802787</v>
+        <v>17.4335608237773</v>
       </c>
       <c r="D3" t="n">
-        <v>0.57404082297464</v>
+        <v>0.573903827456795</v>
       </c>
     </row>
     <row r="4">
@@ -704,10 +704,10 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>17.3894839929906</v>
+        <v>17.3856622419682</v>
       </c>
       <c r="D4" t="n">
-        <v>1.78427516910463</v>
+        <v>1.78393921753448</v>
       </c>
     </row>
     <row r="5">
@@ -718,10 +718,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>9.33859538197771</v>
+        <v>9.34193401787575</v>
       </c>
       <c r="D5" t="n">
-        <v>0.606558385367057</v>
+        <v>0.606789967741097</v>
       </c>
     </row>
     <row r="6">
@@ -732,10 +732,10 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>8.36211780916747</v>
+        <v>8.36354044156639</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8880237394107</v>
+        <v>1.88837296899669</v>
       </c>
     </row>
     <row r="7">
@@ -746,10 +746,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.37829834931532</v>
+        <v>6.37743089234223</v>
       </c>
       <c r="D7" t="n">
-        <v>0.201632562265746</v>
+        <v>0.201584535645552</v>
       </c>
     </row>
     <row r="8">
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>6.0952094129783</v>
+        <v>6.09481794786706</v>
       </c>
       <c r="D8"/>
     </row>
@@ -772,10 +772,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>3.22608947813918</v>
+        <v>3.22543327786321</v>
       </c>
       <c r="D9" t="n">
-        <v>0.652462783436685</v>
+        <v>0.65231206138855</v>
       </c>
     </row>
     <row r="10">
@@ -786,10 +786,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>2.61567542300022</v>
+        <v>2.61572166037823</v>
       </c>
       <c r="D10" t="n">
-        <v>0.266309172716062</v>
+        <v>0.266328161330401</v>
       </c>
     </row>
     <row r="11">
@@ -800,10 +800,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>2.12221346618614</v>
+        <v>2.12151181288669</v>
       </c>
       <c r="D11" t="n">
-        <v>0.588657670421057</v>
+        <v>0.588465550326627</v>
       </c>
     </row>
     <row r="12">
@@ -814,10 +814,10 @@
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>1.27604330034489</v>
+        <v>1.27570358577485</v>
       </c>
       <c r="D12" t="n">
-        <v>0.286174586870707</v>
+        <v>0.286113399427014</v>
       </c>
     </row>
     <row r="13">
@@ -828,10 +828,10 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>1.13570354228655</v>
+        <v>1.13533792434292</v>
       </c>
       <c r="D13" t="n">
-        <v>0.295003082334226</v>
+        <v>0.294899459749859</v>
       </c>
     </row>
     <row r="14">
@@ -842,10 +842,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>0.842819608971247</v>
+        <v>0.843016143430554</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0557464320292799</v>
+        <v>0.0557795981523561</v>
       </c>
     </row>
     <row r="15">
@@ -856,10 +856,10 @@
         <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>0.564474994923797</v>
+        <v>0.564279560192745</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0340832466395912</v>
+        <v>0.0340714462052048</v>
       </c>
     </row>
     <row r="16">
@@ -870,10 +870,10 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>0.528587605318643</v>
+        <v>0.528564616265621</v>
       </c>
       <c r="D16" t="n">
-        <v>0.155918437664913</v>
+        <v>0.155860553194976</v>
       </c>
     </row>
     <row r="17">
@@ -884,10 +884,10 @@
         <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>0.198168603278418</v>
+        <v>0.198099992572837</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0102348477225202</v>
+        <v>0.0102313041736828</v>
       </c>
     </row>
     <row r="18">
@@ -898,10 +898,10 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>0.144123624177585</v>
+        <v>0.144073725135143</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0849243589434293</v>
+        <v>0.0848949561011439</v>
       </c>
     </row>
     <row r="19">
@@ -912,7 +912,7 @@
         <v>29</v>
       </c>
       <c r="C19" t="n">
-        <v>0.125162894608455</v>
+        <v>0.125138873055433</v>
       </c>
       <c r="D19"/>
     </row>
@@ -924,10 +924,10 @@
         <v>26</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0889305135628142</v>
+        <v>0.0889659391173463</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0193712470556227</v>
+        <v>0.0193723438294962</v>
       </c>
     </row>
     <row r="21">
@@ -938,7 +938,7 @@
         <v>38</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0300252950484096</v>
+        <v>0.0300148995738265</v>
       </c>
       <c r="D21"/>
     </row>
@@ -950,7 +950,7 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0300252950484096</v>
+        <v>0.0300148995738265</v>
       </c>
       <c r="D22"/>
     </row>
@@ -987,10 +987,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>23.208697606913</v>
+        <v>23.207771839438</v>
       </c>
       <c r="D2" t="n">
-        <v>1.20734204165949</v>
+        <v>1.20719583557395</v>
       </c>
     </row>
     <row r="3">
@@ -1001,10 +1001,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>18.7585675464447</v>
+        <v>18.7596754229218</v>
       </c>
       <c r="D3" t="n">
-        <v>0.445227623743765</v>
+        <v>0.445256521377909</v>
       </c>
     </row>
     <row r="4">
@@ -1015,10 +1015,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>15.4088131875933</v>
+        <v>15.4088719795948</v>
       </c>
       <c r="D4" t="n">
-        <v>10.7345361992899</v>
+        <v>10.7344944659556</v>
       </c>
     </row>
     <row r="5">
@@ -1029,10 +1029,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>8.27218139624052</v>
+        <v>8.27101045526418</v>
       </c>
       <c r="D5" t="n">
-        <v>1.36968109620548</v>
+        <v>1.36954730085311</v>
       </c>
     </row>
     <row r="6">
@@ -1043,10 +1043,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>5.75200313986558</v>
+        <v>5.75290790518388</v>
       </c>
       <c r="D6" t="n">
-        <v>1.01899653575214</v>
+        <v>1.01917258605361</v>
       </c>
     </row>
     <row r="7">
@@ -1057,10 +1057,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.68965562659846</v>
+        <v>5.69001356082827</v>
       </c>
       <c r="D7" t="n">
-        <v>0.104055190092079</v>
+        <v>0.104069088706042</v>
       </c>
     </row>
     <row r="8">
@@ -1071,10 +1071,10 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>5.50235662250732</v>
+        <v>5.50252043016617</v>
       </c>
       <c r="D8" t="n">
-        <v>0.800444125543568</v>
+        <v>0.80046181295353</v>
       </c>
     </row>
     <row r="9">
@@ -1085,10 +1085,10 @@
         <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>4.34393527695431</v>
+        <v>4.34320640356764</v>
       </c>
       <c r="D9" t="n">
-        <v>1.10234302665655</v>
+        <v>1.10215673471252</v>
       </c>
     </row>
     <row r="10">
@@ -1099,10 +1099,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8326121058502</v>
+        <v>2.83259050834335</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0375308611696348</v>
+        <v>0.0375284299568896</v>
       </c>
     </row>
     <row r="11">
@@ -1113,10 +1113,10 @@
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>2.72315175441127</v>
+        <v>2.72301279020991</v>
       </c>
       <c r="D11" t="n">
-        <v>0.119683381183223</v>
+        <v>0.119670820428728</v>
       </c>
     </row>
     <row r="12">
@@ -1127,10 +1127,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>1.73603927064758</v>
+        <v>1.73634246894241</v>
       </c>
       <c r="D12" t="n">
-        <v>0.137986526107818</v>
+        <v>0.138006835212184</v>
       </c>
     </row>
     <row r="13">
@@ -1141,10 +1141,10 @@
         <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>1.58574655495638</v>
+        <v>1.5857200763407</v>
       </c>
       <c r="D13" t="n">
-        <v>0.149916665967348</v>
+        <v>0.149933979851808</v>
       </c>
     </row>
     <row r="14">
@@ -1155,10 +1155,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>1.14559929153654</v>
+        <v>1.14591544718196</v>
       </c>
       <c r="D14" t="n">
-        <v>0.096593645700778</v>
+        <v>0.0966134880695889</v>
       </c>
     </row>
     <row r="15">
@@ -1169,10 +1169,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1313777084094</v>
+        <v>1.13107877908915</v>
       </c>
       <c r="D15" t="n">
-        <v>0.438306876347372</v>
+        <v>0.438166274567279</v>
       </c>
     </row>
     <row r="16">
@@ -1183,10 +1183,10 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>0.533191579369875</v>
+        <v>0.533244440897158</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0473778828666499</v>
+        <v>0.0473843566599068</v>
       </c>
     </row>
     <row r="17">
@@ -1197,10 +1197,10 @@
         <v>38</v>
       </c>
       <c r="C17" t="n">
-        <v>0.335446007240345</v>
+        <v>0.335502608919009</v>
       </c>
       <c r="D17" t="n">
-        <v>0.145391150819068</v>
+        <v>0.145399331381891</v>
       </c>
     </row>
     <row r="18">
@@ -1211,10 +1211,10 @@
         <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>0.313011764481159</v>
+        <v>0.313003479629514</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0264669082796906</v>
+        <v>0.0264561600207882</v>
       </c>
     </row>
     <row r="19">
@@ -1225,10 +1225,10 @@
         <v>26</v>
       </c>
       <c r="C19" t="n">
-        <v>0.253850907049785</v>
+        <v>0.253812213615222</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07776340641984</v>
+        <v>0.0777507059732587</v>
       </c>
     </row>
     <row r="20">
@@ -1239,10 +1239,10 @@
         <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>0.164086084687455</v>
+        <v>0.164103314192489</v>
       </c>
       <c r="D20" t="n">
-        <v>0.100158054529747</v>
+        <v>0.100180123502046</v>
       </c>
     </row>
     <row r="21">
@@ -1253,7 +1253,7 @@
         <v>29</v>
       </c>
       <c r="C21" t="n">
-        <v>0.152516179850445</v>
+        <v>0.152530179595588</v>
       </c>
       <c r="D21"/>
     </row>
@@ -1265,10 +1265,10 @@
         <v>34</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0980842454091233</v>
+        <v>0.0980799672171447</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0230756382404663</v>
+        <v>0.0230733844377137</v>
       </c>
     </row>
     <row r="23">
@@ -1279,7 +1279,7 @@
         <v>20</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0437381858883574</v>
+        <v>0.0437387712383516</v>
       </c>
       <c r="D23"/>
     </row>
@@ -1291,7 +1291,7 @@
         <v>39</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00657407331009671</v>
+        <v>0.00657693619591377</v>
       </c>
       <c r="D24"/>
     </row>
@@ -1303,7 +1303,7 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00438194189213154</v>
+        <v>0.00438501071358667</v>
       </c>
       <c r="D25"/>
     </row>
@@ -1315,7 +1315,7 @@
         <v>31</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00438194189213154</v>
+        <v>0.00438501071358667</v>
       </c>
       <c r="D26"/>
     </row>
@@ -1719,10 +1719,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>24.6421608383319</v>
+        <v>24.6417854302772</v>
       </c>
       <c r="D2" t="n">
-        <v>4.50858756758852</v>
+        <v>4.50850291956916</v>
       </c>
     </row>
     <row r="3">
@@ -1733,10 +1733,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>21.9561628285138</v>
+        <v>21.9557849726509</v>
       </c>
       <c r="D3" t="n">
-        <v>1.16771398525829</v>
+        <v>1.16769782773181</v>
       </c>
     </row>
     <row r="4">
@@ -1747,10 +1747,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>19.2655397706116</v>
+        <v>19.2658310749008</v>
       </c>
       <c r="D4" t="n">
-        <v>0.801037083083817</v>
+        <v>0.801053720061133</v>
       </c>
     </row>
     <row r="5">
@@ -1761,10 +1761,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.8557823044562</v>
+        <v>5.85590244379546</v>
       </c>
       <c r="D5" t="n">
-        <v>0.163137066026689</v>
+        <v>0.163138527581659</v>
       </c>
     </row>
     <row r="6">
@@ -1775,10 +1775,10 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>5.64193695488102</v>
+        <v>5.64180376429859</v>
       </c>
       <c r="D6" t="n">
-        <v>1.11225319868185</v>
+        <v>1.11217301857517</v>
       </c>
     </row>
     <row r="7">
@@ -1789,10 +1789,10 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>5.54204949466641</v>
+        <v>5.5422000955275</v>
       </c>
       <c r="D7" t="n">
-        <v>1.05968322937623</v>
+        <v>1.05970997848961</v>
       </c>
     </row>
     <row r="8">
@@ -1803,10 +1803,10 @@
         <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>3.93840198783546</v>
+        <v>3.93853124820496</v>
       </c>
       <c r="D8" t="n">
-        <v>2.37820589277897</v>
+        <v>2.37830413975467</v>
       </c>
     </row>
     <row r="9">
@@ -1817,10 +1817,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>2.68983581567514</v>
+        <v>2.68972901058529</v>
       </c>
       <c r="D9" t="n">
-        <v>0.324633621661211</v>
+        <v>0.324586081290426</v>
       </c>
     </row>
     <row r="10">
@@ -1831,10 +1831,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>2.11425113709016</v>
+        <v>2.11456979523719</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0630137464579822</v>
+        <v>0.0630184558174494</v>
       </c>
     </row>
     <row r="11">
@@ -1845,10 +1845,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>1.64273042181408</v>
+        <v>1.64289298050545</v>
       </c>
       <c r="D11" t="n">
-        <v>0.024766852070001</v>
+        <v>0.0247685597634855</v>
       </c>
     </row>
     <row r="12">
@@ -1859,10 +1859,10 @@
         <v>38</v>
       </c>
       <c r="C12" t="n">
-        <v>1.14667551612367</v>
+        <v>1.1465334653637</v>
       </c>
       <c r="D12" t="n">
-        <v>0.369766800613695</v>
+        <v>0.36969012059224</v>
       </c>
     </row>
     <row r="13">
@@ -1873,10 +1873,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>0.956395560811265</v>
+        <v>0.956500761814801</v>
       </c>
       <c r="D13" t="n">
-        <v>0.101961225414945</v>
+        <v>0.101967492441141</v>
       </c>
     </row>
     <row r="14">
@@ -1887,10 +1887,10 @@
         <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>0.867045093700098</v>
+        <v>0.867042172327682</v>
       </c>
       <c r="D14" t="n">
-        <v>0.40737851693052</v>
+        <v>0.40737673228615</v>
       </c>
     </row>
     <row r="15">
@@ -1901,10 +1901,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>0.85322716181884</v>
+        <v>0.853300423066121</v>
       </c>
       <c r="D15" t="n">
-        <v>0.041449296587042</v>
+        <v>0.041446295080044</v>
       </c>
     </row>
     <row r="16">
@@ -1915,10 +1915,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.583402176979545</v>
+        <v>0.583290982760341</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0870314764808729</v>
+        <v>0.0870157783826704</v>
       </c>
     </row>
     <row r="17">
@@ -1929,10 +1929,10 @@
         <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>0.580951198999283</v>
+        <v>0.580955967893585</v>
       </c>
       <c r="D17" t="n">
-        <v>0.159803789662683</v>
+        <v>0.15980181421233</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>46</v>
       </c>
       <c r="C18" t="n">
-        <v>0.561396773370258</v>
+        <v>0.561284058446422</v>
       </c>
       <c r="D18"/>
     </row>
@@ -1955,10 +1955,10 @@
         <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>0.407956245260099</v>
+        <v>0.407987245009878</v>
       </c>
       <c r="D19" t="n">
-        <v>0.04072813612845</v>
+        <v>0.0407363638337707</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>29</v>
       </c>
       <c r="C20" t="n">
-        <v>0.249306340048411</v>
+        <v>0.249311435523764</v>
       </c>
       <c r="D20" t="n">
-        <v>0.026880090038289</v>
+        <v>0.0268774857163241</v>
       </c>
     </row>
     <row r="21">
@@ -1983,7 +1983,7 @@
         <v>28</v>
       </c>
       <c r="C21" t="n">
-        <v>0.222556886622985</v>
+        <v>0.22251479576491</v>
       </c>
       <c r="D21"/>
     </row>
@@ -1995,7 +1995,7 @@
         <v>31</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0794954454718848</v>
+        <v>0.0794804603356408</v>
       </c>
       <c r="D22"/>
     </row>
@@ -2007,10 +2007,10 @@
         <v>34</v>
       </c>
       <c r="C23" t="n">
-        <v>0.063016756916131</v>
+        <v>0.0630217691918993</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0106182411349641</v>
+        <v>0.0106206001393996</v>
       </c>
     </row>
     <row r="24">
@@ -2021,10 +2021,10 @@
         <v>26</v>
       </c>
       <c r="C24" t="n">
-        <v>0.051623866740213</v>
+        <v>0.0516379046782591</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0104755880492871</v>
+        <v>0.0104789957127142</v>
       </c>
     </row>
     <row r="25">
@@ -2035,7 +2035,7 @@
         <v>39</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0286275448625279</v>
+        <v>0.0286216562756727</v>
       </c>
       <c r="D25"/>
     </row>
@@ -2047,10 +2047,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0256296166140272</v>
+        <v>0.0256188408789521</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0052826036674671</v>
+        <v>0.00527685889155468</v>
       </c>
     </row>
     <row r="27">
@@ -2061,7 +2061,7 @@
         <v>20</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0215354993342044</v>
+        <v>0.0215518136787733</v>
       </c>
       <c r="D27"/>
     </row>
@@ -2073,7 +2073,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00769163117802357</v>
+        <v>0.00769723967014162</v>
       </c>
       <c r="D28"/>
     </row>
@@ -2085,7 +2085,7 @@
         <v>25</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00461513127313722</v>
+        <v>0.00461819133621055</v>
       </c>
       <c r="D29"/>
     </row>
@@ -2122,10 +2122,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>21.2485385492539</v>
+        <v>21.2458563989728</v>
       </c>
       <c r="D2" t="n">
-        <v>1.22320616283503</v>
+        <v>1.22297045627264</v>
       </c>
     </row>
     <row r="3">
@@ -2136,10 +2136,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>19.8741580235539</v>
+        <v>19.8722980417864</v>
       </c>
       <c r="D3" t="n">
-        <v>1.08247297210186</v>
+        <v>1.08232234927472</v>
       </c>
     </row>
     <row r="4">
@@ -2150,10 +2150,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>17.7241798195007</v>
+        <v>17.7224537820169</v>
       </c>
       <c r="D4" t="n">
-        <v>4.54736451659128</v>
+        <v>4.54672531155237</v>
       </c>
     </row>
     <row r="5">
@@ -2164,10 +2164,10 @@
         <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>12.5118933543116</v>
+        <v>12.5158221148857</v>
       </c>
       <c r="D5" t="n">
-        <v>4.84513813620268</v>
+        <v>4.84664378215444</v>
       </c>
     </row>
     <row r="6">
@@ -2178,10 +2178,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>10.6290535606668</v>
+        <v>10.6283808772554</v>
       </c>
       <c r="D6" t="n">
-        <v>5.72148293638644</v>
+        <v>5.72085521364488</v>
       </c>
     </row>
     <row r="7">
@@ -2192,7 +2192,7 @@
         <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>5.12700882116796</v>
+        <v>5.12663012137111</v>
       </c>
       <c r="D7"/>
     </row>
@@ -2204,10 +2204,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>4.5410657193669</v>
+        <v>4.54254025821407</v>
       </c>
       <c r="D8" t="n">
-        <v>1.26372211027965</v>
+        <v>1.26424553476954</v>
       </c>
     </row>
     <row r="9">
@@ -2218,10 +2218,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>3.42924529730402</v>
+        <v>3.4306325226418</v>
       </c>
       <c r="D9" t="n">
-        <v>1.30875082780457</v>
+        <v>1.30926703969254</v>
       </c>
     </row>
     <row r="10">
@@ -2232,10 +2232,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>1.21751116830729</v>
+        <v>1.2177090508129</v>
       </c>
       <c r="D10" t="n">
-        <v>0.489497778370004</v>
+        <v>0.489615016945174</v>
       </c>
     </row>
     <row r="11">
@@ -2246,10 +2246,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>1.09845515103157</v>
+        <v>1.09861161623602</v>
       </c>
       <c r="D11" t="n">
-        <v>0.259735777881981</v>
+        <v>0.259767490523437</v>
       </c>
     </row>
     <row r="12">
@@ -2260,10 +2260,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0764610187463</v>
+        <v>1.07669850745551</v>
       </c>
       <c r="D12" t="n">
-        <v>0.186974950143159</v>
+        <v>0.18702418051521</v>
       </c>
     </row>
     <row r="13">
@@ -2274,10 +2274,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>1.00397858421297</v>
+        <v>1.003900417609</v>
       </c>
       <c r="D13" t="n">
-        <v>0.163119185613959</v>
+        <v>0.163084629387419</v>
       </c>
     </row>
     <row r="14">
@@ -2288,10 +2288,10 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>0.272068552038335</v>
+        <v>0.272095187481516</v>
       </c>
       <c r="D14" t="n">
-        <v>0.112442581800846</v>
+        <v>0.112472967401727</v>
       </c>
     </row>
     <row r="15">
@@ -2302,7 +2302,7 @@
         <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>0.106510209713172</v>
+        <v>0.106529229357992</v>
       </c>
       <c r="D15"/>
     </row>
@@ -2314,7 +2314,7 @@
         <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0745489076284746</v>
+        <v>0.0745232685650044</v>
       </c>
       <c r="D16"/>
     </row>
@@ -2326,7 +2326,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0447297899376656</v>
+        <v>0.0447144063464139</v>
       </c>
       <c r="D17"/>
     </row>
@@ -2338,7 +2338,7 @@
         <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0205934732585021</v>
+        <v>0.0206041989915073</v>
       </c>
       <c r="D18"/>
     </row>
@@ -2375,10 +2375,10 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>56.2950113123006</v>
+        <v>56.3041081219849</v>
       </c>
       <c r="D2" t="n">
-        <v>13.8490255669441</v>
+        <v>13.856182263946</v>
       </c>
     </row>
     <row r="3">
@@ -2389,10 +2389,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>17.0508572343531</v>
+        <v>17.0352886501756</v>
       </c>
       <c r="D3" t="n">
-        <v>4.68457221441722</v>
+        <v>4.67777158284229</v>
       </c>
     </row>
     <row r="4">
@@ -2403,10 +2403,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>8.97414045002143</v>
+        <v>8.97376302770651</v>
       </c>
       <c r="D4" t="n">
-        <v>2.23722456511995</v>
+        <v>2.23691437036538</v>
       </c>
     </row>
     <row r="5">
@@ -2417,10 +2417,10 @@
         <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>4.65985259507985</v>
+        <v>4.66228845333324</v>
       </c>
       <c r="D5" t="n">
-        <v>3.20270178727532</v>
+        <v>3.20458350215252</v>
       </c>
     </row>
     <row r="6">
@@ -2431,10 +2431,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.95563362159775</v>
+        <v>2.95631754482207</v>
       </c>
       <c r="D6" t="n">
-        <v>0.166350486782069</v>
+        <v>0.166443705551338</v>
       </c>
     </row>
     <row r="7">
@@ -2445,10 +2445,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2.92746868843593</v>
+        <v>2.92799332344778</v>
       </c>
       <c r="D7" t="n">
-        <v>0.114129339263368</v>
+        <v>0.114145615268467</v>
       </c>
     </row>
     <row r="8">
@@ -2459,10 +2459,10 @@
         <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>2.07571960745581</v>
+        <v>2.07617088760931</v>
       </c>
       <c r="D8" t="n">
-        <v>0.495033498552083</v>
+        <v>0.495069019223064</v>
       </c>
     </row>
     <row r="9">
@@ -2473,10 +2473,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>1.98068645471414</v>
+        <v>1.98260103785225</v>
       </c>
       <c r="D9" t="n">
-        <v>0.40990712214849</v>
+        <v>0.410246235998562</v>
       </c>
     </row>
     <row r="10">
@@ -2487,10 +2487,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>0.967041921835672</v>
+        <v>0.967424695406141</v>
       </c>
       <c r="D10" t="n">
-        <v>0.137633057761389</v>
+        <v>0.137743280417042</v>
       </c>
     </row>
     <row r="11">
@@ -2501,10 +2501,10 @@
         <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>0.653944782403579</v>
+        <v>0.653790508001574</v>
       </c>
       <c r="D11" t="n">
-        <v>0.133944302900671</v>
+        <v>0.133970579529824</v>
       </c>
     </row>
     <row r="12">
@@ -2515,10 +2515,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>0.42055134000046</v>
+        <v>0.420978721028352</v>
       </c>
       <c r="D12" t="n">
-        <v>0.251217866740883</v>
+        <v>0.251600768850808</v>
       </c>
     </row>
     <row r="13">
@@ -2529,10 +2529,10 @@
         <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>0.294797111390009</v>
+        <v>0.294801554152728</v>
       </c>
       <c r="D13" t="n">
-        <v>0.060127286461208</v>
+        <v>0.0601038972054638</v>
       </c>
     </row>
     <row r="14">
@@ -2543,7 +2543,7 @@
         <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>0.273245290917606</v>
+        <v>0.273220773321349</v>
       </c>
       <c r="D14"/>
     </row>
@@ -2555,10 +2555,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>0.168256946602726</v>
+        <v>0.168249505706103</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0369109208262652</v>
+        <v>0.0368418965963167</v>
       </c>
     </row>
     <row r="16">
@@ -2569,10 +2569,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.110220518298119</v>
+        <v>0.110260935136766</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0450243073135336</v>
+        <v>0.0450239683206631</v>
       </c>
     </row>
     <row r="17">
@@ -2583,10 +2583,10 @@
         <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0905129096455505</v>
+        <v>0.0906268818335357</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0213347951269941</v>
+        <v>0.0213609609007617</v>
       </c>
     </row>
     <row r="18">
@@ -2597,7 +2597,7 @@
         <v>26</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0374081938479166</v>
+        <v>0.0373818914578821</v>
       </c>
       <c r="D18"/>
     </row>
@@ -2609,7 +2609,7 @@
         <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0344805445865737</v>
+        <v>0.0345245264127755</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2623,10 +2623,10 @@
         <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>0.030170476513252</v>
+        <v>0.0302089606111786</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00304767836202143</v>
+        <v>0.00305156584296595</v>
       </c>
     </row>
   </sheetData>
@@ -2662,10 +2662,10 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>39.7281014519403</v>
+        <v>39.7290616830707</v>
       </c>
       <c r="D2" t="n">
-        <v>6.21860820764229</v>
+        <v>6.21835232915755</v>
       </c>
     </row>
     <row r="3">
@@ -2676,10 +2676,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>34.8879985888077</v>
+        <v>34.8859603682263</v>
       </c>
       <c r="D3" t="n">
-        <v>4.42073812416722</v>
+        <v>4.42043960561398</v>
       </c>
     </row>
     <row r="4">
@@ -2690,10 +2690,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>7.53251208659025</v>
+        <v>7.53238581525108</v>
       </c>
       <c r="D4" t="n">
-        <v>0.237454364070223</v>
+        <v>0.237447338734724</v>
       </c>
     </row>
     <row r="5">
@@ -2704,10 +2704,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>5.91242411014396</v>
+        <v>5.91280287303072</v>
       </c>
       <c r="D5" t="n">
-        <v>0.512420520758894</v>
+        <v>0.51247295122876</v>
       </c>
     </row>
     <row r="6">
@@ -2718,10 +2718,10 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4.44575576170417</v>
+        <v>4.44623453436161</v>
       </c>
       <c r="D6" t="n">
-        <v>0.630523071027679</v>
+        <v>0.63055259443331</v>
       </c>
     </row>
     <row r="7">
@@ -2732,10 +2732,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>3.25694228270683</v>
+        <v>3.25710668864576</v>
       </c>
       <c r="D7" t="n">
-        <v>0.70733559831466</v>
+        <v>0.707350658262006</v>
       </c>
     </row>
     <row r="8">
@@ -2746,10 +2746,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.14997350271633</v>
+        <v>1.15002814576828</v>
       </c>
       <c r="D8" t="n">
-        <v>0.640721303037778</v>
+        <v>0.640757070135462</v>
       </c>
     </row>
     <row r="9">
@@ -2760,7 +2760,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>0.918428526744664</v>
+        <v>0.918331540824173</v>
       </c>
       <c r="D9"/>
     </row>
@@ -2772,10 +2772,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>0.558108885552207</v>
+        <v>0.558162676090998</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0461198226177086</v>
+        <v>0.0461237017220785</v>
       </c>
     </row>
     <row r="11">
@@ -2786,10 +2786,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>0.494833544322251</v>
+        <v>0.494917936870067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0431730031535043</v>
+        <v>0.043185765399925</v>
       </c>
     </row>
     <row r="12">
@@ -2800,10 +2800,10 @@
         <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2535018465008</v>
+        <v>0.253525157028426</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0546702359334213</v>
+        <v>0.0546684509143556</v>
       </c>
     </row>
     <row r="13">
@@ -2814,10 +2814,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>0.201017799609721</v>
+        <v>0.201066748336308</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0166007935472507</v>
+        <v>0.016605692705767</v>
       </c>
     </row>
     <row r="14">
@@ -2828,10 +2828,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>0.149049513109839</v>
+        <v>0.149076724973757</v>
       </c>
       <c r="D14" t="n">
-        <v>0.022773446583883</v>
+        <v>0.0227812590279868</v>
       </c>
     </row>
     <row r="15">
@@ -2842,10 +2842,10 @@
         <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>0.108401006922979</v>
+        <v>0.108387807070915</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0395979660187865</v>
+        <v>0.0395979486402563</v>
       </c>
     </row>
     <row r="16">
@@ -2856,7 +2856,7 @@
         <v>25</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0846707889820255</v>
+        <v>0.0846647635257898</v>
       </c>
       <c r="D16"/>
     </row>
@@ -2868,10 +2868,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0830568856388914</v>
+        <v>0.0830291559691872</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00740641882260892</v>
+        <v>0.00740165586562154</v>
       </c>
     </row>
     <row r="18">
@@ -2882,7 +2882,7 @@
         <v>29</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0603012976389215</v>
+        <v>0.0603064817301813</v>
       </c>
       <c r="D18"/>
     </row>
@@ -2894,10 +2894,10 @@
         <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0500354950193752</v>
+        <v>0.0500356743516428</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0267642568796029</v>
+        <v>0.0267683469819272</v>
       </c>
     </row>
     <row r="20">
@@ -2908,10 +2908,10 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0437340857696056</v>
+        <v>0.0437491351519284</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0110594125551018</v>
+        <v>0.0110653480533512</v>
       </c>
     </row>
     <row r="21">
@@ -2922,10 +2922,10 @@
         <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0433029130768202</v>
+        <v>0.0433099303780374</v>
       </c>
       <c r="D21" t="n">
-        <v>0.011123392364013</v>
+        <v>0.0111281360177655</v>
       </c>
     </row>
     <row r="22">
@@ -2936,7 +2936,7 @@
         <v>30</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0222428218635845</v>
+        <v>0.0222527924706864</v>
       </c>
       <c r="D22"/>
     </row>
@@ -2948,7 +2948,7 @@
         <v>31</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0121851199534034</v>
+        <v>0.0121795150074924</v>
       </c>
       <c r="D23"/>
     </row>
@@ -2960,7 +2960,7 @@
         <v>32</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00342168468528117</v>
+        <v>0.00342385186597158</v>
       </c>
       <c r="D24"/>
     </row>
@@ -3152,10 +3152,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>91.3398672624444</v>
+        <v>91.3388555763495</v>
       </c>
       <c r="D2" t="n">
-        <v>0.861894170816569</v>
+        <v>0.862083393122336</v>
       </c>
     </row>
     <row r="3">
@@ -3166,10 +3166,10 @@
         <v>34</v>
       </c>
       <c r="C3" t="n">
-        <v>4.29739103414817</v>
+        <v>4.2998423207784</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0933524972452613</v>
+        <v>0.0933985187150417</v>
       </c>
     </row>
     <row r="4">
@@ -3180,10 +3180,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>2.57546103239077</v>
+        <v>2.57620868287384</v>
       </c>
       <c r="D4" t="n">
-        <v>0.234792745253268</v>
+        <v>0.234970077300637</v>
       </c>
     </row>
     <row r="5">
@@ -3194,10 +3194,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>0.74281337850058</v>
+        <v>0.741563473474212</v>
       </c>
       <c r="D5" t="n">
-        <v>0.49049152785471</v>
+        <v>0.489687992578949</v>
       </c>
     </row>
     <row r="6">
@@ -3208,10 +3208,10 @@
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>0.298005242007987</v>
+        <v>0.297697170490835</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0245469511332483</v>
+        <v>0.0245026224151622</v>
       </c>
     </row>
     <row r="7">
@@ -3222,10 +3222,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>0.233212573726985</v>
+        <v>0.23305415970703</v>
       </c>
       <c r="D7" t="n">
-        <v>0.111575935118184</v>
+        <v>0.111513697356389</v>
       </c>
     </row>
     <row r="8">
@@ -3236,7 +3236,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>0.219769260139959</v>
+        <v>0.219623369698133</v>
       </c>
       <c r="D8"/>
     </row>
@@ -3248,7 +3248,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>0.081013606389594</v>
+        <v>0.0810849869124129</v>
       </c>
       <c r="D9"/>
     </row>
@@ -3260,10 +3260,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0781988407569468</v>
+        <v>0.0780182178083647</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0103276745277303</v>
+        <v>0.0103038197620185</v>
       </c>
     </row>
     <row r="11">
@@ -3274,10 +3274,10 @@
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0625588957431237</v>
+        <v>0.0624143977927732</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00844884085840169</v>
+        <v>0.00842932580506875</v>
       </c>
     </row>
     <row r="12">
@@ -3288,10 +3288,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0447621133500903</v>
+        <v>0.044693130754824</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0189029136531948</v>
+        <v>0.0188349213869587</v>
       </c>
     </row>
     <row r="13">
@@ -3302,10 +3302,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0224394212781726</v>
+        <v>0.02243082212351</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0000681580412900505</v>
+        <v>0.0000985696922639011</v>
       </c>
     </row>
     <row r="14">
@@ -3316,7 +3316,7 @@
         <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00450733912334368</v>
+        <v>0.00451369123599265</v>
       </c>
       <c r="D14"/>
     </row>
@@ -3353,10 +3353,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>57.3281405082253</v>
+        <v>57.3281477801791</v>
       </c>
       <c r="D2" t="n">
-        <v>40.3536957324513</v>
+        <v>40.3536922096008</v>
       </c>
     </row>
     <row r="3">
@@ -3367,7 +3367,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>31.1608311737856</v>
+        <v>31.1608281680983</v>
       </c>
       <c r="D3"/>
     </row>
@@ -3379,7 +3379,7 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>8.10635960191601</v>
+        <v>8.10635394396169</v>
       </c>
       <c r="D4"/>
     </row>
@@ -3391,7 +3391,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>2.98313940681246</v>
+        <v>2.98314090517806</v>
       </c>
       <c r="D5"/>
     </row>
@@ -3403,7 +3403,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>0.42152930926069</v>
+        <v>0.421529202582811</v>
       </c>
       <c r="D6"/>
     </row>
@@ -3440,10 +3440,10 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>94.0187702741291</v>
+        <v>94.0396963929599</v>
       </c>
       <c r="D2" t="n">
-        <v>29.8363407254187</v>
+        <v>29.8417603709548</v>
       </c>
     </row>
     <row r="3">
@@ -3454,10 +3454,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>2.46890703144531</v>
+        <v>2.46278487288434</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08710525321409</v>
+        <v>0.0870575126095609</v>
       </c>
     </row>
     <row r="4">
@@ -3468,10 +3468,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>0.760679645127287</v>
+        <v>0.759402820259848</v>
       </c>
       <c r="D4" t="n">
-        <v>0.116497598478017</v>
+        <v>0.116513645389048</v>
       </c>
     </row>
     <row r="5">
@@ -3482,10 +3482,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>0.662619659931421</v>
+        <v>0.658718649738598</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0196785784858147</v>
+        <v>0.019562734423141</v>
       </c>
     </row>
     <row r="6">
@@ -3496,10 +3496,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>0.570724366816388</v>
+        <v>0.567713398141494</v>
       </c>
       <c r="D6" t="n">
-        <v>0.388472017279955</v>
+        <v>0.386431784779191</v>
       </c>
     </row>
     <row r="7">
@@ -3510,10 +3510,10 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>0.444117302840861</v>
+        <v>0.441503066619031</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0165552300912905</v>
+        <v>0.0164577879062501</v>
       </c>
     </row>
     <row r="8">
@@ -3524,10 +3524,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>0.365483940765809</v>
+        <v>0.364752632660417</v>
       </c>
       <c r="D8" t="n">
-        <v>0.254843093468926</v>
+        <v>0.254346979051385</v>
       </c>
     </row>
     <row r="9">
@@ -3538,10 +3538,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>0.199192433748206</v>
+        <v>0.198019888344106</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0222951020193061</v>
+        <v>0.0221638051926366</v>
       </c>
     </row>
     <row r="10">
@@ -3552,10 +3552,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>0.190898338682771</v>
+        <v>0.190677332152804</v>
       </c>
       <c r="D10" t="n">
-        <v>0.064368226732903</v>
+        <v>0.0644377307378925</v>
       </c>
     </row>
     <row r="11">
@@ -3566,10 +3566,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>0.105694253405797</v>
+        <v>0.105071841369835</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00655903092408336</v>
+        <v>0.00652037608813461</v>
       </c>
     </row>
     <row r="12">
@@ -3580,10 +3580,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0818111706369464</v>
+        <v>0.0813294628481086</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0110361643657286</v>
+        <v>0.0109712459676748</v>
       </c>
     </row>
     <row r="13">
@@ -3594,10 +3594,10 @@
         <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0320131673348304</v>
+        <v>0.031824490762082</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00288790137493388</v>
+        <v>0.00287098879932759</v>
       </c>
     </row>
     <row r="14">
@@ -3608,10 +3608,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0315049450563881</v>
+        <v>0.0313196978493678</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00421072009354453</v>
+        <v>0.00418595584490087</v>
       </c>
     </row>
     <row r="15">
@@ -3622,10 +3622,10 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02388287249898</v>
+        <v>0.023742169843383</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00467103303641761</v>
+        <v>0.00464364622282581</v>
       </c>
     </row>
     <row r="16">
@@ -3636,7 +3636,7 @@
         <v>30</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0116872199753333</v>
+        <v>0.0116185841261627</v>
       </c>
       <c r="D16"/>
     </row>
@@ -3648,7 +3648,7 @@
         <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00965475140130624</v>
+        <v>0.00959795172690207</v>
       </c>
       <c r="D17"/>
     </row>
@@ -3660,7 +3660,7 @@
         <v>19</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00711406054883688</v>
+        <v>0.00707210905824045</v>
       </c>
       <c r="D18"/>
     </row>
@@ -3672,7 +3672,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="n">
-        <v>0.00711406054883688</v>
+        <v>0.00707210905824045</v>
       </c>
       <c r="D19"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>29</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00609782626182335</v>
+        <v>0.00606189719778185</v>
       </c>
       <c r="D20"/>
     </row>
@@ -3696,7 +3696,7 @@
         <v>40</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00203267884389815</v>
+        <v>0.00202063239926062</v>
       </c>
       <c r="D21"/>
     </row>
@@ -3733,10 +3733,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>29.5596890511849</v>
+        <v>29.5598568310332</v>
       </c>
       <c r="D2" t="n">
-        <v>1.57484095938842</v>
+        <v>1.57499445086972</v>
       </c>
     </row>
     <row r="3">
@@ -3747,10 +3747,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>18.1689234804074</v>
+        <v>18.1673264885753</v>
       </c>
       <c r="D3" t="n">
-        <v>0.432739320612276</v>
+        <v>0.432718841054423</v>
       </c>
     </row>
     <row r="4">
@@ -3761,10 +3761,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>11.2867641756239</v>
+        <v>11.2870459326145</v>
       </c>
       <c r="D4" t="n">
-        <v>7.79747841092047</v>
+        <v>7.79773733744146</v>
       </c>
     </row>
     <row r="5">
@@ -3775,10 +3775,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>8.0097858428954</v>
+        <v>8.01115393796449</v>
       </c>
       <c r="D5" t="n">
-        <v>1.60905995460106</v>
+        <v>1.60936124402573</v>
       </c>
     </row>
     <row r="6">
@@ -3789,10 +3789,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>6.77989306604406</v>
+        <v>6.77881974051897</v>
       </c>
       <c r="D6" t="n">
-        <v>1.16354430973066</v>
+        <v>1.16335433995446</v>
       </c>
     </row>
     <row r="7">
@@ -3803,10 +3803,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>5.0238598649609</v>
+        <v>5.02543647216513</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0962055789564638</v>
+        <v>0.0962524733982313</v>
       </c>
     </row>
     <row r="8">
@@ -3817,10 +3817,10 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>4.17942439810022</v>
+        <v>4.17865556908465</v>
       </c>
       <c r="D8" t="n">
-        <v>0.629474802709262</v>
+        <v>0.629336454614041</v>
       </c>
     </row>
     <row r="9">
@@ -3831,10 +3831,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>3.96557918239868</v>
+        <v>3.96573075921366</v>
       </c>
       <c r="D9" t="n">
-        <v>0.113591911080886</v>
+        <v>0.113586087641846</v>
       </c>
     </row>
     <row r="10">
@@ -3845,10 +3845,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>2.78975080444999</v>
+        <v>2.78941399814897</v>
       </c>
       <c r="D10" t="n">
-        <v>0.237114443555658</v>
+        <v>0.237065455423461</v>
       </c>
     </row>
     <row r="11">
@@ -3859,10 +3859,10 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>2.76752140081153</v>
+        <v>2.76760900747935</v>
       </c>
       <c r="D11" t="n">
-        <v>0.821765152469481</v>
+        <v>0.821789923031818</v>
       </c>
     </row>
     <row r="12">
@@ -3873,10 +3873,10 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>1.94620304946784</v>
+        <v>1.94666949763768</v>
       </c>
       <c r="D12" t="n">
-        <v>0.107228840321645</v>
+        <v>0.107272471208542</v>
       </c>
     </row>
     <row r="13">
@@ -3887,10 +3887,10 @@
         <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>1.54503415439421</v>
+        <v>1.54499986880777</v>
       </c>
       <c r="D13" t="n">
-        <v>0.250650727927502</v>
+        <v>0.250653674269885</v>
       </c>
     </row>
     <row r="14">
@@ -3901,10 +3901,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0631987894026</v>
+        <v>1.06308706922884</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0927383291354896</v>
+        <v>0.0927261331216983</v>
       </c>
     </row>
     <row r="15">
@@ -3915,10 +3915,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>0.935661132298646</v>
+        <v>0.93565860860922</v>
       </c>
       <c r="D15" t="n">
-        <v>0.403450995764877</v>
+        <v>0.403441789026877</v>
       </c>
     </row>
     <row r="16">
@@ -3929,10 +3929,10 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>0.524260671449889</v>
+        <v>0.524152306972405</v>
       </c>
       <c r="D16" t="n">
-        <v>0.323530587624025</v>
+        <v>0.323469312291106</v>
       </c>
     </row>
     <row r="17">
@@ -3943,10 +3943,10 @@
         <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>0.297590307020918</v>
+        <v>0.297553863194058</v>
       </c>
       <c r="D17" t="n">
-        <v>0.105589392066944</v>
+        <v>0.105597733144794</v>
       </c>
     </row>
     <row r="18">
@@ -3957,10 +3957,10 @@
         <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>0.26521902396207</v>
+        <v>0.26530472662009</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0206940780505517</v>
+        <v>0.0206946981035593</v>
       </c>
     </row>
     <row r="19">
@@ -3971,10 +3971,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.25487580782696</v>
+        <v>0.254814837259604</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0191447711243624</v>
+        <v>0.0191428227718087</v>
       </c>
     </row>
     <row r="20">
@@ -3985,7 +3985,7 @@
         <v>29</v>
       </c>
       <c r="C20" t="n">
-        <v>0.253991756615979</v>
+        <v>0.253949371069562</v>
       </c>
       <c r="D20"/>
     </row>
@@ -3997,10 +3997,10 @@
         <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>0.173577872758271</v>
+        <v>0.173568969952148</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0241654040245121</v>
+        <v>0.0241653376278085</v>
       </c>
     </row>
     <row r="22">
@@ -4011,7 +4011,7 @@
         <v>11</v>
       </c>
       <c r="C22" t="n">
-        <v>0.11370582480294</v>
+        <v>0.113712742732618</v>
       </c>
       <c r="D22"/>
     </row>
@@ -4023,7 +4023,7 @@
         <v>20</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0741321783585579</v>
+        <v>0.0741080584124175</v>
       </c>
       <c r="D23"/>
     </row>
@@ -4035,7 +4035,7 @@
         <v>42</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0213581647638638</v>
+        <v>0.0213713427054722</v>
       </c>
       <c r="D24"/>
     </row>
